--- a/data/trans_dic/P32C-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,26</t>
+          <t>1,32; 9,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,77</t>
+          <t>3,57; 11,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,15</t>
+          <t>1,81; 8,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,6</t>
+          <t>0,9; 6,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,74</t>
+          <t>2,41; 7,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,37</t>
+          <t>1,79; 6,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,4</t>
+          <t>0,93; 5,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,56</t>
+          <t>0,58; 3,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,59</t>
+          <t>1,2; 5,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,21</t>
+          <t>0,94; 4,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,56</t>
+          <t>0,39; 2,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,0</t>
+          <t>0,86; 3,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,13</t>
+          <t>0,78; 4,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,11</t>
+          <t>0,27; 2,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,41</t>
+          <t>0,87; 3,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,38</t>
+          <t>0,83; 5,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,0</t>
+          <t>0,55; 4,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,75</t>
+          <t>0,37; 3,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,02</t>
+          <t>0,81; 4,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,45</t>
+          <t>0,37; 3,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,33</t>
+          <t>0,37; 2,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,29</t>
+          <t>0,71; 6,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,06</t>
+          <t>0,0; 16,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,65</t>
+          <t>0,5; 5,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,44</t>
+          <t>0,48; 4,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,04</t>
+          <t>0,57; 6,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,73</t>
+          <t>0,29; 2,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,95</t>
+          <t>0,84; 3,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,87</t>
+          <t>1,14; 4,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,89</t>
+          <t>1,19; 4,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,47</t>
+          <t>1,16; 4,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,35</t>
+          <t>0,94; 4,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,37</t>
+          <t>0,8; 3,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,83</t>
+          <t>0,79; 2,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,04</t>
+          <t>0,81; 2,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,33</t>
+          <t>0,56; 3,16</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,79</t>
+          <t>0,67; 2,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,41</t>
+          <t>0,71; 3,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,25</t>
+          <t>0,26; 2,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,67</t>
+          <t>0,23; 2,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,44</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,41</t>
+          <t>0,64; 2,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,6</t>
+          <t>0,5; 2,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,84</t>
+          <t>0,43; 1,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,14</t>
+          <t>0,17; 1,81</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,65</t>
+          <t>1,34; 2,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,8</t>
+          <t>1,43; 2,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,25</t>
+          <t>1,11; 2,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,74</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,83</t>
+          <t>0,39; 1,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,22</t>
+          <t>0,19; 1,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,83</t>
+          <t>0,33; 1,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,15</t>
+          <t>1,14; 2,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,94</t>
+          <t>1,02; 1,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,67</t>
+          <t>0,88; 1,67</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,55</t>
+          <t>0,71; 1,53</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1887; 12065</t>
+          <t>1935; 13329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6018; 20629</t>
+          <t>6260; 19905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3215; 16357</t>
+          <t>3240; 15525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5733</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5990</t>
+          <t>0; 6012</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6994</t>
+          <t>0; 7151</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2869; 14496</t>
+          <t>1974; 13778</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7198; 22060</t>
+          <t>6857; 21280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4742; 18069</t>
+          <t>5068; 18818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1492</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2005; 12349</t>
+          <t>2123; 12350</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1877; 10998</t>
+          <t>1786; 11378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3171; 14882</t>
+          <t>3185; 15792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2712</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1526</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2029; 12706</t>
+          <t>2833; 12961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1736; 11726</t>
+          <t>1805; 11099</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3190; 14723</t>
+          <t>3146; 14098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4755</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6409</t>
+          <t>0; 5559</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1619; 7654</t>
+          <t>1443; 8720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2075</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6018</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3492</t>
+          <t>0; 3679</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4061</t>
+          <t>0; 5232</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>861; 6831</t>
+          <t>864; 8632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2246; 9405</t>
+          <t>2404; 9749</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1973; 12791</t>
+          <t>1977; 13776</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1027; 9344</t>
+          <t>1026; 9246</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>681; 6676</t>
+          <t>660; 6233</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8519</t>
+          <t>0; 7164</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3021</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2463; 14820</t>
+          <t>2972; 15533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1031; 9469</t>
+          <t>1004; 9955</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2042</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>775; 7034</t>
+          <t>1123; 6957</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4511</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>892; 8067</t>
+          <t>914; 8799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1904</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1267</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8540</t>
+          <t>0; 7910</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1990</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1746</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2375</t>
+          <t>0; 2046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 9440</t>
+          <t>0; 9488</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>909; 8477</t>
+          <t>914; 9797</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2437</t>
+          <t>0; 2490</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6577</t>
+          <t>0; 6047</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 5345</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5073</t>
+          <t>0; 6086</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>859; 7330</t>
+          <t>797; 7518</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4919</t>
+          <t>0; 5159</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1899</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>526; 5825</t>
+          <t>552; 6135</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>876; 8364</t>
+          <t>881; 7958</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5337</t>
+          <t>0; 5355</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5080</t>
+          <t>0; 5715</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2248; 10324</t>
+          <t>2201; 10223</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2872; 14075</t>
+          <t>3303; 14275</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4371; 15303</t>
+          <t>4694; 16824</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4895; 17096</t>
+          <t>4450; 16375</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3056; 13381</t>
+          <t>2886; 14718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6010</t>
+          <t>0; 5050</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6405</t>
+          <t>0; 4997</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 16412</t>
+          <t>0; 17070</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2743; 14159</t>
+          <t>3345; 14364</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5012; 17036</t>
+          <t>4788; 17335</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5916; 19528</t>
+          <t>5189; 18177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3983; 23611</t>
+          <t>3973; 22347</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3304; 13776</t>
+          <t>3282; 13348</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3200; 15523</t>
+          <t>3224; 16981</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1131; 10002</t>
+          <t>1138; 10893</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>660; 7416</t>
+          <t>649; 7455</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>998; 8261</t>
+          <t>0; 7950</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5098</t>
+          <t>0; 5512</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7587</t>
+          <t>0; 7692</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 1387</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5406; 17647</t>
+          <t>4722; 17674</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4269; 17387</t>
+          <t>3333; 18276</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2838; 12801</t>
+          <t>2971; 13801</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>658; 8079</t>
+          <t>645; 6847</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>24534; 49733</t>
+          <t>25161; 49639</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29656; 56954</t>
+          <t>29063; 54709</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22488; 44608</t>
+          <t>22072; 45121</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11182; 27422</t>
+          <t>12648; 27601</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3529; 16377</t>
+          <t>3470; 17009</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1001; 9173</t>
+          <t>997; 8400</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2921; 13756</t>
+          <t>2095; 12883</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3608; 18783</t>
+          <t>3393; 18061</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31280; 59731</t>
+          <t>31509; 57626</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31615; 59712</t>
+          <t>31268; 59237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27679; 52044</t>
+          <t>27460; 51938</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19245; 40527</t>
+          <t>18427; 39892</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32C-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,12</t>
+          <t>1,26; 8,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 11,35</t>
+          <t>3,61; 11,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,69</t>
+          <t>1,99; 9,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,27</t>
+          <t>0,9; 6,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,47</t>
+          <t>2,53; 7,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,63</t>
+          <t>1,66; 6,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,4</t>
+          <t>0,89; 5,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,68</t>
+          <t>0,58; 3,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,93</t>
+          <t>1,19; 5,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,3</t>
+          <t>0,71; 4,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,42</t>
+          <t>0,41; 2,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,83</t>
+          <t>0,89; 4,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,71</t>
+          <t>0,94; 5,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,66</t>
+          <t>0,27; 2,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,54</t>
+          <t>0,89; 3,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,79</t>
+          <t>1,0; 5,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,95</t>
+          <t>0,55; 5,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,5</t>
+          <t>0,34; 3,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,21</t>
+          <t>0,81; 4,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,63</t>
+          <t>0,36; 3,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,3</t>
+          <t>0,35; 2,4</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,86</t>
+          <t>0,71; 6,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,72</t>
+          <t>0,0; 15,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,37</t>
+          <t>0,5; 5,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,56</t>
+          <t>0,47; 4,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,36</t>
+          <t>0,56; 6,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,6</t>
+          <t>0,29; 2,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,91</t>
+          <t>0,84; 4,1</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,94</t>
+          <t>1,15; 4,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,28</t>
+          <t>1,0; 3,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,28</t>
+          <t>1,15; 4,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,78</t>
+          <t>0,82; 3,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,22 +1582,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,73; 7,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,42</t>
+          <t>0,83; 3,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,83</t>
+          <t>0,81; 2,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,16</t>
+          <t>1,23; 4,39</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,71</t>
+          <t>0,66; 2,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,73</t>
+          <t>0,71; 3,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,45</t>
+          <t>0,26; 2,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,69</t>
+          <t>0,23; 2,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,42; 3,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,22 +1737,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,41</t>
+          <t>0,64; 2,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,73</t>
+          <t>0,5; 2,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,98</t>
+          <t>0,32; 1,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,81</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,64</t>
+          <t>1,3; 2,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,69</t>
+          <t>1,5; 2,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,28</t>
+          <t>1,12; 2,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,78; 1,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,9</t>
+          <t>0,41; 1,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,81</t>
+          <t>0,1; 0,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,14</t>
+          <t>0,19; 1,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,76</t>
+          <t>0,56; 2,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,08</t>
+          <t>1,13; 2,09</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,93</t>
+          <t>1,04; 1,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,67</t>
+          <t>0,86; 1,67</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,53</t>
+          <t>0,85; 1,76</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1935; 13329</t>
+          <t>1845; 12317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6260; 19905</t>
+          <t>6333; 20425</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3240; 15525</t>
+          <t>3559; 16322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4055</t>
+          <t>0; 5688</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6012</t>
+          <t>0; 5162</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7151</t>
+          <t>0; 6509</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1974; 13778</t>
+          <t>1981; 14934</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6857; 21280</t>
+          <t>7208; 21642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5068; 18818</t>
+          <t>4717; 18097</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2123; 12350</t>
+          <t>2045; 12204</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1786; 11378</t>
+          <t>1793; 11035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3185; 15792</t>
+          <t>3174; 15148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2833; 12961</t>
+          <t>2135; 12784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1805; 11099</t>
+          <t>1866; 11671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3146; 14098</t>
+          <t>3276; 14994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5685</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5464</t>
+          <t>0; 4381</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5559</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1443; 8720</t>
+          <t>1759; 9474</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4656</t>
+          <t>0; 5566</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3679</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5232</t>
+          <t>0; 5198</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>864; 8632</t>
+          <t>866; 7785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2404; 9749</t>
+          <t>2453; 10467</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3334</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1977; 13776</t>
+          <t>2382; 13947</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1026; 9246</t>
+          <t>1020; 9630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>660; 6233</t>
+          <t>683; 6250</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7164</t>
+          <t>0; 7250</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2972; 15533</t>
+          <t>3000; 15994</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1004; 9955</t>
+          <t>996; 9173</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1123; 6957</t>
+          <t>1201; 8203</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>914; 8799</t>
+          <t>915; 8945</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7910</t>
+          <t>0; 7479</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 9488</t>
+          <t>0; 9173</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>914; 9797</t>
+          <t>918; 9261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2490</t>
+          <t>0; 2472</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5131</t>
         </is>
       </c>
     </row>
@@ -3249,27 +3249,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6047</t>
+          <t>0; 7006</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 4568</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6086</t>
+          <t>0; 5889</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>797; 7518</t>
+          <t>772; 6789</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>0; 5801</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>552; 6135</t>
+          <t>546; 6213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>881; 7958</t>
+          <t>873; 7860</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5355</t>
+          <t>0; 5291</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5715</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2201; 10223</t>
+          <t>2181; 10701</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>13864</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3303; 14275</t>
+          <t>3314; 14023</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4694; 16824</t>
+          <t>3937; 15104</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4450; 16375</t>
+          <t>4395; 17445</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2886; 14718</t>
+          <t>2860; 13610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5050</t>
+          <t>0; 5543</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4997</t>
+          <t>0; 5020</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 17070</t>
+          <t>1726; 16976</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3345; 14364</t>
+          <t>3494; 14652</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4788; 17335</t>
+          <t>4765; 17317</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5189; 18177</t>
+          <t>5186; 18353</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3973; 22347</t>
+          <t>7207; 25669</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>3018</t>
         </is>
       </c>
     </row>
@@ -3665,37 +3665,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3282; 13348</t>
+          <t>3262; 13594</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3224; 16981</t>
+          <t>3249; 17127</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1138; 10893</t>
+          <t>1142; 9856</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>649; 7455</t>
+          <t>718; 8326</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7950</t>
+          <t>1006; 8392</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 5706</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7692</t>
+          <t>0; 7577</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,22 +3705,22 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4722; 17674</t>
+          <t>4665; 16634</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3333; 18276</t>
+          <t>3359; 17909</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2971; 13801</t>
+          <t>2215; 13766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>645; 6847</t>
+          <t>0; 8117</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>31502</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>25161; 49639</t>
+          <t>24416; 48743</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29063; 54709</t>
+          <t>30521; 56367</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22072; 45121</t>
+          <t>22204; 44470</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12648; 27601</t>
+          <t>13181; 29087</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3470; 17009</t>
+          <t>3702; 16168</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>997; 8400</t>
+          <t>992; 8150</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2095; 12883</t>
+          <t>2095; 12297</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3393; 18061</t>
+          <t>5046; 23533</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>31509; 57626</t>
+          <t>31482; 57897</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31268; 59237</t>
+          <t>31979; 58695</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27460; 51938</t>
+          <t>26676; 51967</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>18427; 39892</t>
+          <t>21866; 45461</t>
         </is>
       </c>
     </row>
